--- a/cds_files/Houston_CDS_2024-2025.xlsx
+++ b/cds_files/Houston_CDS_2024-2025.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="C3" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.82</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="5">
